--- a/diseases/d167/2020-2025.xlsx
+++ b/diseases/d167/2020-2025.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12092,7 +12092,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12488,7 +12488,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13280,7 +13280,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14072,7 +14072,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14864,7 +14864,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15656,7 +15656,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16052,7 +16052,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16448,7 +16448,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16844,7 +16844,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17240,7 +17240,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18032,7 +18032,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18428,7 +18428,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18824,7 +18824,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19220,7 +19220,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20012,7 +20012,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20556,7 +20556,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -21100,7 +21100,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -22188,7 +22188,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22732,7 +22732,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -23276,7 +23276,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23820,7 +23820,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -24364,7 +24364,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -24908,7 +24908,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -25452,7 +25452,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -25996,7 +25996,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -26540,7 +26540,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27084,7 +27084,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -27628,7 +27628,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -28172,7 +28172,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -28716,7 +28716,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -29260,7 +29260,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -29804,7 +29804,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -30348,7 +30348,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -30892,7 +30892,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -31436,7 +31436,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -31980,7 +31980,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -32524,7 +32524,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">

--- a/diseases/d167/2020-2025.xlsx
+++ b/diseases/d167/2020-2025.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12092,7 +12092,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12488,7 +12488,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13280,7 +13280,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14072,7 +14072,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14864,7 +14864,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15656,7 +15656,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16052,7 +16052,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16448,7 +16448,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16844,7 +16844,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17240,7 +17240,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18032,7 +18032,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18428,7 +18428,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18824,7 +18824,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19220,7 +19220,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20012,7 +20012,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20556,7 +20556,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -21100,7 +21100,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -22188,7 +22188,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22732,7 +22732,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -23276,7 +23276,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23820,7 +23820,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -24364,7 +24364,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -24908,7 +24908,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -25452,7 +25452,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -25996,7 +25996,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -26540,7 +26540,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27084,7 +27084,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -27628,7 +27628,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -28172,7 +28172,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -28716,7 +28716,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -29260,7 +29260,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -29804,7 +29804,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -30348,7 +30348,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -30892,7 +30892,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -31436,7 +31436,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -31980,7 +31980,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -32524,7 +32524,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">

--- a/diseases/d167/2020-2025.xlsx
+++ b/diseases/d167/2020-2025.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>4</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0.01553772713583637</v>
       </c>
@@ -1161,9 +1158,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -1557,9 +1551,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -1953,9 +1944,6 @@
       <c r="O8" t="n">
         <v>1</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.003884431783959091</v>
       </c>
@@ -2349,9 +2337,6 @@
       <c r="O10" t="n">
         <v>1</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.003884431783959091</v>
       </c>
@@ -2745,9 +2730,6 @@
       <c r="O12" t="n">
         <v>3</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.01165329535187727</v>
       </c>
@@ -3141,9 +3123,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -3537,9 +3516,6 @@
       <c r="O16" t="n">
         <v>2</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0.007768863567918183</v>
       </c>
@@ -3933,9 +3909,6 @@
       <c r="O18" t="n">
         <v>1</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.003884431783959091</v>
       </c>
@@ -4329,9 +4302,6 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
@@ -4725,9 +4695,6 @@
       <c r="O22" t="n">
         <v>3</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0.01165329535187727</v>
       </c>
@@ -5121,9 +5088,6 @@
       <c r="O24" t="n">
         <v>1</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.003884431783959091</v>
       </c>
@@ -5517,9 +5481,6 @@
       <c r="O26" t="n">
         <v>2</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.007705223573322474</v>
       </c>
@@ -5913,9 +5874,6 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
@@ -6309,9 +6267,6 @@
       <c r="O30" t="n">
         <v>1</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.003852611786661237</v>
       </c>
@@ -6705,9 +6660,6 @@
       <c r="O32" t="n">
         <v>2</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.007705223573322474</v>
       </c>
@@ -7101,9 +7053,6 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
@@ -7497,9 +7446,6 @@
       <c r="O36" t="n">
         <v>1</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.003852611786661237</v>
       </c>
@@ -7893,9 +7839,6 @@
       <c r="O38" t="n">
         <v>1</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.003852611786661237</v>
       </c>
@@ -8289,9 +8232,6 @@
       <c r="O40" t="n">
         <v>4</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.01541044714664495</v>
       </c>
@@ -8685,9 +8625,6 @@
       <c r="O42" t="n">
         <v>1</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0.003852611786661237</v>
       </c>
@@ -9081,9 +9018,6 @@
       <c r="O44" t="n">
         <v>1</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0.003852611786661237</v>
       </c>
@@ -9477,9 +9411,6 @@
       <c r="O46" t="n">
         <v>1</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.003852611786661237</v>
       </c>
@@ -9873,9 +9804,6 @@
       <c r="O48" t="n">
         <v>1</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0.003852611786661237</v>
       </c>
@@ -10269,9 +10197,6 @@
       <c r="O50" t="n">
         <v>2</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.007633300954779008</v>
       </c>
@@ -10665,9 +10590,6 @@
       <c r="O52" t="n">
         <v>2</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0.007633300954779008</v>
       </c>
@@ -11061,9 +10983,6 @@
       <c r="O54" t="n">
         <v>1</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0.003816650477389504</v>
       </c>
@@ -11457,9 +11376,6 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
@@ -11853,9 +11769,6 @@
       <c r="O58" t="n">
         <v>1</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0.003816650477389504</v>
       </c>
@@ -12249,9 +12162,6 @@
       <c r="O60" t="n">
         <v>1</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.003816650477389504</v>
       </c>
@@ -12645,9 +12555,6 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
@@ -13041,9 +12948,6 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
@@ -13437,9 +13341,6 @@
       <c r="O66" t="n">
         <v>2</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0.007633300954779008</v>
       </c>
@@ -13833,9 +13734,6 @@
       <c r="O68" t="n">
         <v>4</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0.01526660190955802</v>
       </c>
@@ -14229,9 +14127,6 @@
       <c r="O70" t="n">
         <v>1</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0.003816650477389504</v>
       </c>
@@ -14625,9 +14520,6 @@
       <c r="O72" t="n">
         <v>1</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.003816650477389504</v>
       </c>
@@ -15021,9 +14913,6 @@
       <c r="O74" t="n">
         <v>1</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.003780557680649034</v>
       </c>
@@ -15417,9 +15306,6 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
@@ -15813,9 +15699,6 @@
       <c r="O78" t="n">
         <v>3</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.0113416730419471</v>
       </c>
@@ -16209,9 +16092,6 @@
       <c r="O80" t="n">
         <v>1</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.003780557680649034</v>
       </c>
@@ -16605,9 +16485,6 @@
       <c r="O82" t="n">
         <v>1</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.003780557680649034</v>
       </c>
@@ -17001,9 +16878,6 @@
       <c r="O84" t="n">
         <v>2</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0.007561115361298068</v>
       </c>
@@ -17397,9 +17271,6 @@
       <c r="O86" t="n">
         <v>3</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.0113416730419471</v>
       </c>
@@ -17793,9 +17664,6 @@
       <c r="O88" t="n">
         <v>2</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0.007561115361298068</v>
       </c>
@@ -18189,9 +18057,6 @@
       <c r="O90" t="n">
         <v>2</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.007561115361298068</v>
       </c>
@@ -18585,9 +18450,6 @@
       <c r="O92" t="n">
         <v>2</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0.007561115361298068</v>
       </c>
@@ -18981,9 +18843,6 @@
       <c r="O94" t="n">
         <v>1</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0.003780557680649034</v>
       </c>
@@ -19377,9 +19236,6 @@
       <c r="O96" t="n">
         <v>1</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0.003780557680649034</v>
       </c>
@@ -19773,9 +19629,6 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
@@ -20169,9 +20022,6 @@
       <c r="O100" t="n">
         <v>1</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0.00193357811143172</v>
       </c>
@@ -20317,9 +20167,6 @@
       <c r="O101" t="n">
         <v>1</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0.003743466948275207</v>
       </c>
@@ -20713,9 +20560,6 @@
       <c r="O103" t="n">
         <v>2</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0.00386715622286344</v>
       </c>
@@ -20861,9 +20705,6 @@
       <c r="O104" t="n">
         <v>2</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.007486933896550414</v>
       </c>
@@ -21257,9 +21098,6 @@
       <c r="O106" t="n">
         <v>0</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0</v>
       </c>
@@ -21405,9 +21243,6 @@
       <c r="O107" t="n">
         <v>1</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.003743466948275207</v>
       </c>
@@ -21801,9 +21636,6 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
@@ -21949,9 +21781,6 @@
       <c r="O110" t="n">
         <v>1</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.003743466948275207</v>
       </c>
@@ -22345,9 +22174,6 @@
       <c r="O112" t="n">
         <v>2</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0.00386715622286344</v>
       </c>
@@ -22493,9 +22319,6 @@
       <c r="O113" t="n">
         <v>0</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0</v>
       </c>
@@ -22889,9 +22712,6 @@
       <c r="O115" t="n">
         <v>1</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0.00193357811143172</v>
       </c>
@@ -23037,9 +22857,6 @@
       <c r="O116" t="n">
         <v>0</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0</v>
       </c>
@@ -23433,9 +23250,6 @@
       <c r="O118" t="n">
         <v>1</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.00193357811143172</v>
       </c>
@@ -23581,9 +23395,6 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0</v>
       </c>
@@ -23977,9 +23788,6 @@
       <c r="O121" t="n">
         <v>0</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0</v>
       </c>
@@ -24125,9 +23933,6 @@
       <c r="O122" t="n">
         <v>1</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0.003743466948275207</v>
       </c>
@@ -24521,9 +24326,6 @@
       <c r="O124" t="n">
         <v>3</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0.005800734334295159</v>
       </c>
@@ -24669,9 +24471,6 @@
       <c r="O125" t="n">
         <v>1</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0.003743466948275207</v>
       </c>
@@ -25065,9 +24864,6 @@
       <c r="O127" t="n">
         <v>1</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0.00193357811143172</v>
       </c>
@@ -25213,9 +25009,6 @@
       <c r="O128" t="n">
         <v>1</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0.003743466948275207</v>
       </c>
@@ -25609,9 +25402,6 @@
       <c r="O130" t="n">
         <v>0</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0</v>
       </c>
@@ -25757,9 +25547,6 @@
       <c r="O131" t="n">
         <v>1</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0.003743466948275207</v>
       </c>
@@ -26153,9 +25940,6 @@
       <c r="O133" t="n">
         <v>1</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0.00193357811143172</v>
       </c>
@@ -26301,9 +26085,6 @@
       <c r="O134" t="n">
         <v>1</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0.003707270097537535</v>
       </c>
@@ -26697,9 +26478,6 @@
       <c r="O136" t="n">
         <v>3</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0.005806410836914865</v>
       </c>
@@ -26845,9 +26623,6 @@
       <c r="O137" t="n">
         <v>1</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0.003707270097537535</v>
       </c>
@@ -27241,9 +27016,6 @@
       <c r="O139" t="n">
         <v>1</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0.001935470278971621</v>
       </c>
@@ -27389,9 +27161,6 @@
       <c r="O140" t="n">
         <v>1</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0.003707270097537535</v>
       </c>
@@ -27785,9 +27554,6 @@
       <c r="O142" t="n">
         <v>0</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0</v>
       </c>
@@ -27933,9 +27699,6 @@
       <c r="O143" t="n">
         <v>1</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0.003707270097537535</v>
       </c>
@@ -28329,9 +28092,6 @@
       <c r="O145" t="n">
         <v>1</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0.001935470278971621</v>
       </c>
@@ -28477,9 +28237,6 @@
       <c r="O146" t="n">
         <v>2</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0.00741454019507507</v>
       </c>
@@ -28873,9 +28630,6 @@
       <c r="O148" t="n">
         <v>1</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0.001935470278971621</v>
       </c>
@@ -29021,9 +28775,6 @@
       <c r="O149" t="n">
         <v>3</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0.01112181029261261</v>
       </c>
@@ -29417,9 +29168,6 @@
       <c r="O151" t="n">
         <v>1</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0.001935470278971621</v>
       </c>
@@ -29565,9 +29313,6 @@
       <c r="O152" t="n">
         <v>2</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0.00741454019507507</v>
       </c>
@@ -29961,9 +29706,6 @@
       <c r="O154" t="n">
         <v>0</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0</v>
       </c>
@@ -30109,9 +29851,6 @@
       <c r="O155" t="n">
         <v>0</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0</v>
       </c>
@@ -30505,9 +30244,6 @@
       <c r="O157" t="n">
         <v>0</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>0</v>
       </c>
@@ -30653,9 +30389,6 @@
       <c r="O158" t="n">
         <v>0</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0</v>
       </c>
@@ -31049,9 +30782,6 @@
       <c r="O160" t="n">
         <v>1</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0.001935470278971621</v>
       </c>
@@ -31197,9 +30927,6 @@
       <c r="O161" t="n">
         <v>2</v>
       </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
       <c r="R161" t="n">
         <v>0.00741454019507507</v>
       </c>
@@ -31593,9 +31320,6 @@
       <c r="O163" t="n">
         <v>0</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0</v>
       </c>
@@ -31741,9 +31465,6 @@
       <c r="O164" t="n">
         <v>0</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0</v>
       </c>
@@ -32137,9 +31858,6 @@
       <c r="O166" t="n">
         <v>2</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0.003870940557943243</v>
       </c>
@@ -32285,9 +32003,6 @@
       <c r="O167" t="n">
         <v>0</v>
       </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
       <c r="R167" t="n">
         <v>0</v>
       </c>
@@ -32680,9 +32395,6 @@
       </c>
       <c r="O169" t="n">
         <v>2</v>
-      </c>
-      <c r="Q169" t="n">
-        <v>0</v>
       </c>
       <c r="R169" t="n">
         <v>0.003870940557943243</v>

--- a/diseases/d167/2020-2025.xlsx
+++ b/diseases/d167/2020-2025.xlsx
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -6906,7 +6906,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -7692,7 +7692,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8478,7 +8478,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -8871,7 +8871,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9657,7 +9657,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -10836,7 +10836,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11229,7 +11229,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -11622,7 +11622,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12015,7 +12015,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12408,7 +12408,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -13587,7 +13587,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -13980,7 +13980,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14373,7 +14373,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15159,7 +15159,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -15552,7 +15552,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -15945,7 +15945,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -16338,7 +16338,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -16731,7 +16731,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -17124,7 +17124,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -17517,7 +17517,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -17910,7 +17910,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18303,7 +18303,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -18696,7 +18696,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19089,7 +19089,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -19482,7 +19482,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -19875,7 +19875,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -20413,7 +20413,7 @@
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN102" t="b">
@@ -20951,7 +20951,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -21489,7 +21489,7 @@
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN108" t="b">
@@ -22027,7 +22027,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -22565,7 +22565,7 @@
       </c>
       <c r="AM114" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN114" t="b">
@@ -23103,7 +23103,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -23641,7 +23641,7 @@
       </c>
       <c r="AM120" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN120" t="b">
@@ -24179,7 +24179,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -24717,7 +24717,7 @@
       </c>
       <c r="AM126" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN126" t="b">
@@ -25255,7 +25255,7 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -25793,7 +25793,7 @@
       </c>
       <c r="AM132" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN132" t="b">
@@ -26331,7 +26331,7 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -26869,7 +26869,7 @@
       </c>
       <c r="AM138" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN138" t="b">
@@ -27407,7 +27407,7 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN141" t="b">
@@ -27945,7 +27945,7 @@
       </c>
       <c r="AM144" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN144" t="b">
@@ -28483,7 +28483,7 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -29021,7 +29021,7 @@
       </c>
       <c r="AM150" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN150" t="b">
@@ -29559,7 +29559,7 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN153" t="b">
@@ -30097,7 +30097,7 @@
       </c>
       <c r="AM156" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN156" t="b">
@@ -30635,7 +30635,7 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN159" t="b">
@@ -31173,7 +31173,7 @@
       </c>
       <c r="AM162" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN162" t="b">
@@ -31711,7 +31711,7 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN165" t="b">
@@ -32249,7 +32249,7 @@
       </c>
       <c r="AM168" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN168" t="b">

--- a/diseases/d167/2020-2025.xlsx
+++ b/diseases/d167/2020-2025.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10040,7 +10040,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10433,7 +10433,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10826,7 +10826,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12005,7 +12005,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12398,7 +12398,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13184,7 +13184,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13577,7 +13577,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14363,7 +14363,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14756,7 +14756,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15149,7 +15149,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15542,7 +15542,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -15935,7 +15935,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16328,7 +16328,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16721,7 +16721,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -17900,7 +17900,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18293,7 +18293,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18686,7 +18686,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19079,7 +19079,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19472,7 +19472,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -19865,7 +19865,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20403,7 +20403,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -20941,7 +20941,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21479,7 +21479,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -22017,7 +22017,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22555,7 +22555,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -23093,7 +23093,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23631,7 +23631,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -24169,7 +24169,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -24707,7 +24707,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -25245,7 +25245,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -25783,7 +25783,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -26321,7 +26321,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -26859,7 +26859,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -27397,7 +27397,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -27935,7 +27935,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -28473,7 +28473,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -29011,7 +29011,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -29549,7 +29549,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -30087,7 +30087,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -30625,7 +30625,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -31163,7 +31163,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -31701,7 +31701,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -32239,7 +32239,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
